--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_82_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_82_IN_Piura.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C10" s="31">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>47.77</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>39.55</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>12.67</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>35.6612</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1946,11 +1946,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>31.1413</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>87.33</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>4.5199</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>12.67</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>35.6767</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2254,6 +2254,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2462,6 +2463,7 @@
       <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="17" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -2506,6 +2508,7 @@
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="132" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -3055,11 +3058,11 @@
       </c>
       <c r="B22" s="33">
         <f>SUM(B10:B21)</f>
-        <v/>
+        <v>853.87</v>
       </c>
       <c r="C22" s="23">
         <f>SUM(C10:C21)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
@@ -3069,19 +3072,19 @@
       <c r="E22" s="17" t="inlineStr"/>
       <c r="F22" s="17">
         <f>ROUND(AVERAGE(F10:F21),2)</f>
-        <v/>
+        <v>28.51</v>
       </c>
       <c r="G22" s="22">
         <f>ROUND(AVERAGE(G10:G21),4)</f>
-        <v/>
+        <v>0.5992</v>
       </c>
       <c r="H22" s="23">
         <f>ROUND(AVERAGE(H10:H21),2)</f>
-        <v/>
+        <v>71.82</v>
       </c>
       <c r="I22" s="23">
         <f>ROUND(AVERAGE(I10:I21),2)</f>
-        <v/>
+        <v>19.14</v>
       </c>
     </row>
     <row r="23"/>
